--- a/out/MLP-mamba2_repeat_4_000007.xlsx
+++ b/out/MLP-mamba2_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.358776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000249372580786352</v>
+        <v>-0.0002433204925917089</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.874897556777437</v>
+        <v>2.805125918255472</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.754239186348496</v>
+        <v>5.61458805494301</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4311036902213438</v>
+        <v>0.4206411217893512</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.73769054747507</v>
+        <v>3.646979560863549</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5390198848459939</v>
+        <v>0.525938326747049</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.384695157421089</v>
+        <v>4.278281847938431</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7726824486779369</v>
+        <v>0.7539299345061813</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.39134457489626</v>
+        <v>5.260500526084068</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8266171673120422</v>
+        <v>0.8065556916422403</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.271954441983781</v>
+        <v>6.119738557849992</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8760475849440473</v>
+        <v>0.8547872020584041</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.197495775216682</v>
+        <v>7.022817606318316</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3953439816736134</v>
+        <v>0.3857489004317117</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.1114080175734</v>
+        <v>6.938819213090008</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.190933073342321</v>
+        <v>0.1862997308229416</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.097620133412997</v>
+        <v>6.925365961686533</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09097453790371882</v>
+        <v>0.08876566234552458</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.088483221200744</v>
+        <v>6.916450834461755</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02695475779757305</v>
+        <v>0.02630100976432374</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.051322020762749</v>
+        <v>6.880191412346302</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01782956712621729</v>
+        <v>0.01739713718082558</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.06001255795205</v>
+        <v>6.888670944105668</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00912315162444487</v>
+        <v>0.008901761723021985</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.060418279676984</v>
+        <v>6.889066682195914</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004664905655678081</v>
+        <v>0.004551152834145073</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.060618524750326</v>
+        <v>6.8892619277665</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001750216122947345</v>
+        <v>0.001707830567585098</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.059451270736295</v>
+        <v>6.888122984295696</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009520069336199789</v>
+        <v>0.0009280817602794793</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.059603333392161</v>
+        <v>6.88827118858807</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004559433713238305</v>
+        <v>0.0004448171520160139</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.059562608063562</v>
+        <v>6.888231325594988</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002803469840561617</v>
+        <v>0.0002734592982341164</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.059667143118441</v>
+        <v>6.888333216700267</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001442585278353905</v>
+        <v>0.0001401410512054487</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.059675147401165</v>
+        <v>6.88834090771276</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.69347054165328e-05</v>
+        <v>6.593561228574761e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.358776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.059665664542192</v>
+        <v>6.888331517007114</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.104926959945762e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.059681077098154</v>
+        <v>6.888346370336235</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.059671845761136</v>
+        <v>6.888337252670722</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.059664242778333</v>
+        <v>6.888329786093728</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.059660069606741</v>
+        <v>6.888325530915558</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.05965434732771</v>
+        <v>6.888319808636527</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.059649277972341</v>
+        <v>6.888314739281158</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.059644912998372</v>
+        <v>6.888310374307189</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.059646004244829</v>
+        <v>6.888311465553646</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.059645314637693</v>
+        <v>6.88831077594651</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.059645344950096</v>
+        <v>6.888310806258912</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.059645155497585</v>
+        <v>6.888310616806402</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.059645208544289</v>
+        <v>6.888310669853105</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.059645261590991</v>
+        <v>6.888310722899807</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.059645223700489</v>
+        <v>6.888310685009305</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.059645094872782</v>
+        <v>6.888310556181598</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.059644950888875</v>
+        <v>6.888310412197692</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.05964484479547</v>
+        <v>6.888310306104286</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.059644609874358</v>
+        <v>6.888310071183174</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.059644776592566</v>
+        <v>6.888310237901382</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.059644973623176</v>
+        <v>6.888310434931992</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.059644814483068</v>
+        <v>6.888310275791884</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.358776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.05964485237357</v>
+        <v>6.888310313682386</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.05964504940418</v>
+        <v>6.888310510712996</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.059645026669878</v>
+        <v>6.888310487978695</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.05964487510787</v>
+        <v>6.888310336416687</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.059644799326867</v>
+        <v>6.888310260635683</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.059644897842173</v>
+        <v>6.888310359150989</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.059644905420273</v>
+        <v>6.888310366729089</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.059645170653787</v>
+        <v>6.888310631962603</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.05964487510787</v>
+        <v>6.888310336416687</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.958776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.059645117607083</v>
+        <v>6.8883105789159</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.059645200966187</v>
+        <v>6.888310662275004</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.059645034247979</v>
+        <v>6.888310495556796</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.059645223700489</v>
+        <v>6.888310685009305</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.05964487510787</v>
+        <v>6.888310336416687</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.05964467049916</v>
+        <v>6.888310131807977</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.059644784170666</v>
+        <v>6.888310245479482</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.059644799326867</v>
+        <v>6.888310260635683</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.059644564405755</v>
+        <v>6.888310025714572</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.059644625030558</v>
+        <v>6.888310086339374</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.059644496202851</v>
+        <v>6.888309957511667</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.059644632608658</v>
+        <v>6.888310093917475</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.059644806904967</v>
+        <v>6.888310268213783</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.059644950888875</v>
+        <v>6.888310412197692</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.059644784170666</v>
+        <v>6.888310245479482</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.059644776592566</v>
+        <v>6.888310237901382</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.059644488624751</v>
+        <v>6.888309949933567</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.059644503780952</v>
+        <v>6.888309965089769</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.059644731123964</v>
+        <v>6.88831019243278</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.059644715967762</v>
+        <v>6.888310177276579</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.059644822061168</v>
+        <v>6.888310283369984</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.059644549249554</v>
+        <v>6.888310010558371</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.059644647764859</v>
+        <v>6.888310109073675</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.059644799326867</v>
+        <v>6.888310260635683</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.059644814483068</v>
+        <v>6.888310275791884</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.958776160273009</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.05964487510787</v>
+        <v>6.888310336416687</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.059644973623176</v>
+        <v>6.888310434931992</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.059644806904967</v>
+        <v>6.888310268213783</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.059644761436364</v>
+        <v>6.888310222745181</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.358776160273009</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.059644746280164</v>
+        <v>6.888310207588981</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.059644784170666</v>
+        <v>6.888310245479482</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.059644799326867</v>
+        <v>6.888310260635683</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.059644791748767</v>
+        <v>6.888310253057583</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000007.xlsx
+++ b/out/MLP-mamba2_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.123605319917338</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000249372580786352</v>
+        <v>-0.0001494319654698484</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.874897556777437</v>
+        <v>1.722729789347278</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.754239186348496</v>
+        <v>3.448122759605449</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4311036902213438</v>
+        <v>0.2583310166236635</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.73769054747507</v>
+        <v>2.239742757073317</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5390198848459939</v>
+        <v>0.3229978829971231</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.384695157421089</v>
+        <v>2.627448485837405</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7726824486779369</v>
+        <v>0.4630157708157593</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.39134457489626</v>
+        <v>3.230664752077404</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8266171673120422</v>
+        <v>0.495335160708502</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.271954441983781</v>
+        <v>3.758354195629157</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8760475849440473</v>
+        <v>0.5249554309253132</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.197495775216682</v>
+        <v>4.312968159322113</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3953439816736134</v>
+        <v>0.2369032883115023</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.1114080175734</v>
+        <v>4.261381592422929</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.190933073342321</v>
+        <v>0.1144134602245194</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.097620133412997</v>
+        <v>4.253119460011128</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09097453790371882</v>
+        <v>0.05451460749143844</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.088483221200744</v>
+        <v>4.24764435461997</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02695475779757305</v>
+        <v>0.01615187528877359</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.051322020762749</v>
+        <v>4.22537621574399</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01782956712621729</v>
+        <v>0.01068215634700254</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.06001255795205</v>
+        <v>4.230582141199257</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00912315162444487</v>
+        <v>0.00546480649782139</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.060418279676984</v>
+        <v>4.230823264579126</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004664905655678081</v>
+        <v>0.002793520742139483</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.060618524750326</v>
+        <v>4.230941261195614</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001750216122947345</v>
+        <v>0.001047070034884351</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.059451270736295</v>
+        <v>4.23023976034523</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009520069336199789</v>
+        <v>0.0005683791541947287</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.059603333392161</v>
+        <v>4.23032886253991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004559433713238305</v>
+        <v>0.00027077129284374</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.059562608063562</v>
+        <v>4.230302458625742</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002803469840561617</v>
+        <v>0.000166208190433697</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.059667143118441</v>
+        <v>4.23036317965867</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001442585278353905</v>
+        <v>8.455511670123428e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.059675147401165</v>
+        <v>4.230365982228303</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.69347054165328e-05</v>
+        <v>3.796100462376264e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.059665664542192</v>
+        <v>4.230358292756144</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.104926959945762e-05</v>
+        <v>2.314122031077965e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.059681077098154</v>
+        <v>4.230365595746628</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.598100299746031e-05</v>
+        <v>7.821724054003525e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.059671845761136</v>
+        <v>4.230358079395481</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.059664242778333</v>
+        <v>4.230351572669123</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.059660069606741</v>
+        <v>4.230347068766166</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.05965434732771</v>
+        <v>4.230341635634698</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.059649277972341</v>
+        <v>4.23033658901363</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.059644912998372</v>
+        <v>4.230336907293847</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.059646004244829</v>
+        <v>4.230337998540303</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.059645314637693</v>
+        <v>4.230337308933168</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.059645344950096</v>
+        <v>4.23033733924557</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.059645155497585</v>
+        <v>4.230337149793059</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.059645208544289</v>
+        <v>4.230337202839763</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.059645261590991</v>
+        <v>4.230337255886465</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.059645223700489</v>
+        <v>4.230337217995963</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.059645094872782</v>
+        <v>4.230337089168256</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.059644950888875</v>
+        <v>4.230336945184349</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.05964484479547</v>
+        <v>4.230336839090944</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.059644609874358</v>
+        <v>4.230336604169832</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.059644776592566</v>
+        <v>4.23033677088804</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.059644973623176</v>
+        <v>4.23033696791865</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.059644814483068</v>
+        <v>4.230336808778542</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.358776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.05964485237357</v>
+        <v>4.230336846669044</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.05964504940418</v>
+        <v>4.230337043699654</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.059645026669878</v>
+        <v>4.230337020965353</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.05964487510787</v>
+        <v>4.230336869403344</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.059644799326867</v>
+        <v>4.230336793622341</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.059644897842173</v>
+        <v>4.230336892137647</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.059644905420273</v>
+        <v>4.230336899715747</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.059645170653787</v>
+        <v>4.230337164949261</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.05964487510787</v>
+        <v>4.230336869403344</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.059645117607083</v>
+        <v>4.230337111902557</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.059645200966187</v>
+        <v>4.230337195261662</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.059645034247979</v>
+        <v>4.230337028543453</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.059645223700489</v>
+        <v>4.230337217995963</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.05964487510787</v>
+        <v>4.230336869403344</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.05964467049916</v>
+        <v>4.230336664794634</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.059644784170666</v>
+        <v>4.23033677846614</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.059644799326867</v>
+        <v>4.230336793622341</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.059644564405755</v>
+        <v>4.23033655870123</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.059644625030558</v>
+        <v>4.230336619326032</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.059644496202851</v>
+        <v>4.230336490498325</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.059644632608658</v>
+        <v>4.230336626904132</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.059644806904967</v>
+        <v>4.230336801200441</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.059644950888875</v>
+        <v>4.230336945184349</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.059644784170666</v>
+        <v>4.23033677846614</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.059644776592566</v>
+        <v>4.23033677088804</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.059644488624751</v>
+        <v>4.230336482920225</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.059644503780952</v>
+        <v>4.230336498076426</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.059644731123964</v>
+        <v>4.230336725419438</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.059644715967762</v>
+        <v>4.230336710263236</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.059644822061168</v>
+        <v>4.230336816356642</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.059644549249554</v>
+        <v>4.230336543545028</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.059644647764859</v>
+        <v>4.230336642060333</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.059644799326867</v>
+        <v>4.230336793622341</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.059644814483068</v>
+        <v>4.230336808778542</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.05964487510787</v>
+        <v>4.230336869403344</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.059644973623176</v>
+        <v>4.23033696791865</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.059644806904967</v>
+        <v>4.230336801200441</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.059644761436364</v>
+        <v>4.230336755731838</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.059644746280164</v>
+        <v>4.230336740575638</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.059644784170666</v>
+        <v>4.23033677846614</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.059644799326867</v>
+        <v>4.230336793622341</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.059644791748767</v>
+        <v>4.230336786044241</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000007.xlsx
+++ b/out/MLP-mamba2_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.2692491412162781</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.123605319917338</v>
+        <v>-0.7199999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5304964184761047</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4393822252750397</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1264365315437317</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.524056077003479</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.359517902135849</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3081746995449066</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.1962135881185532</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4822381734848022</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2867859303951263</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.314393013715744</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2626153230667114</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6008615493774414</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.1770402640104294</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.1844336241483688</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.650235870066816</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2392260581254959</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.650235870066816</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4718760251998901</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.2140878140926361</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3094015121459961</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.7450315952301025</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.8402100205421448</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.9272497892379761</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3590338528156281</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4698411226272583</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.650235870066816</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4509981870651245</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3476223349571228</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.2784026861190796</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.8753092288970947</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3489958345890045</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4911113381385803</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4261974692344666</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.171075776219368</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5257642269134521</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5981309413909912</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.924041211605072</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.9870135188102722</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5819294452667236</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.8085760474205017</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001494319654698484</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.722729789347278</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2616722583770752</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.448122759605449</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2583310166236635</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6247140765190125</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.239742757073317</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3229978829971231</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7616984844207764</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.627448485837405</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4630157708157593</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.9575430750846863</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.297446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.230664752077404</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.495335160708502</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.978972852230072</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.297446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.758354195629157</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5249554309253132</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8732157349586487</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.312968159322113</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2369032883115023</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.596519947052002</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.261381592422929</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1144134602245194</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.05995708331465721</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.253119460011128</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05451460749143844</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.05201695114374161</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.24764435461997</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01615187528877359</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.6537129282951355</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.22537621574399</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01068215634700254</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5414938926696777</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.230582141199257</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00546480649782139</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.1350748091936111</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.230823264579126</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002793520742139483</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3123213648796082</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.230941261195614</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001047070034884351</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5870278477668762</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.23023976034523</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005683791541947287</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.518915593624115</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.23032886253991</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.00027077129284374</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.8428975939750671</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.230302458625742</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000166208190433697</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.7044981718063354</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.23036317965867</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.455511670123428e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2162448912858963</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.230365982228303</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.796100462376264e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9829725623130798</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.230358292756144</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.314122031077965e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.2692667841911316</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.230365595746628</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>7.821724054003525e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.06288463622331619</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.230358079395481</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5340690612792969</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.230351572669123</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.1686077564954758</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.230347068766166</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3909412622451782</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.230341635634698</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.9629604816436768</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.23033658901363</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9794638156890869</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.230336907293847</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8412572145462036</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.230337998540303</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.1167932525277138</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.230337308933168</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.0135072898119688</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.23033733924557</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.1645847260951996</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.230337149793059</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3619885742664337</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.230337202839763</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1358949542045593</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.230337255886465</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1673571616411209</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.230337217995963</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1630791127681732</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.230337089168256</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.235154464840889</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.230336945184349</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5019699335098267</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3830098807811737</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.230336839090944</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3936401903629303</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.650235870066816</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.1091761291027069</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.9295787811279297</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.230336604169832</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.8833703994750977</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.23033677088804</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.09504444152116776</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.23033696791865</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4187994003295898</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.230336808778542</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.844307005405426</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.230336846669044</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.6582151055335999</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.230337043699654</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1415074318647385</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.230337020965353</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2523958086967468</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.230336869403344</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.5793027281761169</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.230336793622341</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4506250023841858</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.230336892137647</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.8188010454177856</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.230336899715747</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2609205543994904</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.230337164949261</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.7222480773925781</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.230336869403344</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.8249312043190002</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.230337111902557</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.05350939556956291</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.230337195261662</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.9236454367637634</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.230337028543453</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.04549121484160423</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.230337217995963</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.1436145156621933</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.230336869403344</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.271492213010788</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.230336664794634</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4692842364311218</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.23033677846614</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.08926945179700851</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.230336793622341</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5807833075523376</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.23033655870123</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.1192053034901619</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.230336619326032</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.7351483106613159</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.230336490498325</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.9662299156188965</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.230336626904132</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.587230384349823</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.230336801200441</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1272428780794144</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.230336945184349</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4684479534626007</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.23033677846614</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.03284892812371254</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.23033677088804</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3873538970947266</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.230336482920225</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.8906642198562622</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.230336498076426</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3866486251354218</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.230336725419438</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.8338756561279297</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.230336710263236</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.03649472072720528</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.230336816356642</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.5207718014717102</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.230336543545028</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.8163093328475952</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.230336642060333</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4798870086669922</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.230336793622341</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5148764848709106</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.230336808778542</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5268470048904419</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.629450261592865</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.230336869403344</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2507439255714417</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.23033696791865</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1814946681261063</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.230336801200441</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4064099490642548</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3148353695869446</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.230336755731838</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.5364439487457275</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.230336740575638</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.458763986825943</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.23033677846614</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4289377331733704</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.230336793622341</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4206831455230713</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.230336786044241</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000007.xlsx
+++ b/out/MLP-mamba2_repeat_4_000007.xlsx
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.1962135881185532</v>
+        <v>0.1962136030197144</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2867859303951263</v>
+        <v>0.2867859601974487</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.7199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.2626153230667114</v>
+        <v>0.2626153826713562</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.6008615493774414</v>
+        <v>0.6008616089820862</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3094015121459961</v>
+        <v>0.3094015717506409</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.7450315952301025</v>
+        <v>0.7450315356254578</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3590338528156281</v>
+        <v>0.3590338230133057</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4698411226272583</v>
+        <v>0.4698411524295807</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4509981870651245</v>
+        <v>0.4509981572628021</v>
       </c>
       <c r="JB26" t="n">
         <v>0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3476223349571228</v>
+        <v>0.3476223051548004</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.2784026861190796</v>
+        <v>0.2784026563167572</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3489958345890045</v>
+        <v>0.3489958047866821</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.924041211605072</v>
+        <v>0.9240411520004272</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.9870135188102722</v>
+        <v>0.9870133996009827</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2616722583770752</v>
+        <v>0.2616722881793976</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.596519947052002</v>
+        <v>0.5965201258659363</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.05201695114374161</v>
+        <v>0.05201693996787071</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.5414938926696777</v>
+        <v>0.5414939522743225</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.1350748091936111</v>
+        <v>0.13507479429245</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.5799999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5870278477668762</v>
+        <v>0.587027907371521</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.518915593624115</v>
+        <v>0.5189156532287598</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.7044981718063354</v>
+        <v>0.7044982314109802</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2162448912858963</v>
+        <v>0.2162448614835739</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.2692667841911316</v>
+        <v>0.2692667543888092</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.06288463622331619</v>
+        <v>0.06288465112447739</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.5340690612792969</v>
+        <v>0.5340691208839417</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.1686077564954758</v>
+        <v>0.1686077415943146</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.8412572145462036</v>
+        <v>0.8412570953369141</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.1167932525277138</v>
+        <v>0.1167932227253914</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0135072898119688</v>
+        <v>0.01350728329271078</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1645847260951996</v>
+        <v>0.1645848304033279</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3619885742664337</v>
+        <v>0.3619886040687561</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1358949542045593</v>
+        <v>0.1358949840068817</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1630791127681732</v>
+        <v>0.1630790680646896</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.5019699335098267</v>
+        <v>0.5019704699516296</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.1199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3830098807811737</v>
+        <v>0.3830099105834961</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.1199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3936401903629303</v>
+        <v>0.3936401307582855</v>
       </c>
       <c r="JB77" t="n">
         <v>0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1091761291027069</v>
+        <v>0.1091761738061905</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.09504444152116776</v>
+        <v>0.09504447877407074</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4187994003295898</v>
+        <v>0.4187994301319122</v>
       </c>
       <c r="JB82" t="n">
         <v>0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.844307005405426</v>
+        <v>0.8443070650100708</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1415074318647385</v>
+        <v>0.1415074616670609</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.5793027281761169</v>
+        <v>0.5793026685714722</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.8188010454177856</v>
+        <v>0.8188011646270752</v>
       </c>
       <c r="JB89" t="n">
         <v>0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.05350939556956291</v>
+        <v>0.05350940674543381</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.08926945179700851</v>
+        <v>0.08926943689584732</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.5807833075523376</v>
+        <v>0.5807832479476929</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1192053034901619</v>
+        <v>0.1192052885890007</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1272428780794144</v>
+        <v>0.1272428929805756</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3866486251354218</v>
+        <v>0.3866486549377441</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.03649472072720528</v>
+        <v>0.03649471327662468</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.629450261592865</v>
+        <v>0.6294502019882202</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2507439255714417</v>
+        <v>0.250743955373764</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.4064099490642548</v>
+        <v>0.4064100086688995</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.5364439487457275</v>
+        <v>0.5364438891410828</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.458763986825943</v>
+        <v>0.4587641060352325</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4289377331733704</v>
+        <v>0.4289376735687256</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.4399999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4206831455230713</v>
+        <v>0.4206831157207489</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1600000000000001</v>
